--- a/outputs/monitor_xlsx/20260302.xlsx
+++ b/outputs/monitor_xlsx/20260302.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2331,7 +2331,7 @@
         <v>-106265</v>
       </c>
       <c r="N23" t="n">
-        <v>37.24</v>
+        <v>30.7</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2389,6 +2389,59 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-6.65</v>
+      </c>
+      <c r="E25" t="n">
+        <v>604</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>-195</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-248</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-72</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-111</v>
+      </c>
+      <c r="J25" t="n">
+        <v>35</v>
+      </c>
+      <c r="K25" t="n">
+        <v>332</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1689</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-8887</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260302.xlsx
+++ b/outputs/monitor_xlsx/20260302.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,215 +526,232 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>35095.09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+2.22%</t>
-        </is>
-      </c>
+          <t>-0.90%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5294.4$</t>
+          <t>316.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+1.22%</t>
-        </is>
-      </c>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.38</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+0.43%</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8137.36</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.48%</t>
-        </is>
-      </c>
+          <t>+2.22%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>5294.4$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+7.96%</t>
-        </is>
-      </c>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-389.89億</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>125.36億</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>626.81億</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>73.46億</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1469.25億</t>
-        </is>
-      </c>
+          <t>31.38</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+0.43%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>83.22億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>33.09億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>165.45億</t>
-        </is>
-      </c>
+          <t>8137.36</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>133.33%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>161.75%</t>
-        </is>
-      </c>
+          <t>21.44</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+7.96%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-432.14億</t>
-        </is>
-      </c>
+          <t>71.23$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+6.28%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,52 +761,173 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14171口</t>
-        </is>
-      </c>
+          <t>-389.89億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11909口</t>
+          <t>125.36億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>626.81億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>73.46億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1469.25億</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>投信現貨</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>83.22億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>33.09億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>165.45億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-432.14億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14171口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>11909口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-22.25億</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-52.15億</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-260.73億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>-17.57億</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>-351.35億</t>
         </is>
@@ -878,6 +1016,10 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -972,7 +1114,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>161.75%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -999,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1017,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1034,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1113,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1181,13 +1316,13 @@
         <v>-101500</v>
       </c>
       <c r="H4" t="n">
-        <v>-153600</v>
+        <v>-154795</v>
       </c>
       <c r="I4" t="n">
         <v>3214</v>
       </c>
       <c r="J4" t="n">
-        <v>30200</v>
+        <v>21700</v>
       </c>
       <c r="K4" t="n">
         <v>54837</v>
@@ -1196,20 +1331,12 @@
         <v>8643</v>
       </c>
       <c r="M4" t="n">
-        <v>39383</v>
+        <v>32009</v>
       </c>
       <c r="N4" t="n">
         <v>-4134246</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1218,41 +1345,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3792</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-967</v>
+        <v>-723</v>
       </c>
       <c r="H5" t="n">
-        <v>75</v>
+        <v>3148</v>
+      </c>
+      <c r="I5" t="n">
+        <v>39</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-302</v>
       </c>
       <c r="K5" t="n">
-        <v>2004</v>
+        <v>173</v>
       </c>
       <c r="L5" t="n">
-        <v>9643</v>
+        <v>2936</v>
       </c>
       <c r="M5" t="n">
-        <v>49034</v>
+        <v>11898</v>
       </c>
       <c r="N5" t="n">
-        <v>-27513</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>-78749</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1261,12 +1400,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1275,47 +1414,39 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1030</v>
+        <v>1425</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-3.74</v>
+        <v>-0.35</v>
       </c>
       <c r="F6" t="n">
-        <v>3792</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>-723</v>
+        <v>15569</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>210</v>
       </c>
       <c r="H6" t="n">
-        <v>3870</v>
+        <v>2005</v>
       </c>
       <c r="I6" t="n">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="J6" t="n">
-        <v>-898</v>
+        <v>2486</v>
       </c>
       <c r="K6" t="n">
-        <v>173</v>
+        <v>337</v>
       </c>
       <c r="L6" t="n">
-        <v>2936</v>
+        <v>6395</v>
       </c>
       <c r="M6" t="n">
-        <v>14736</v>
+        <v>26382</v>
       </c>
       <c r="N6" t="n">
-        <v>-78749</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>-648849</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1324,12 +1455,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1338,47 +1469,39 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1425</v>
+        <v>1975</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.35</v>
+        <v>-1</v>
       </c>
       <c r="F7" t="n">
-        <v>15569</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>210</v>
+        <v>57404</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>-19539</v>
       </c>
       <c r="H7" t="n">
-        <v>3451</v>
+        <v>-33001</v>
       </c>
       <c r="I7" t="n">
-        <v>162</v>
+        <v>2624</v>
       </c>
       <c r="J7" t="n">
-        <v>3170</v>
+        <v>7753</v>
       </c>
       <c r="K7" t="n">
-        <v>337</v>
+        <v>1215</v>
       </c>
       <c r="L7" t="n">
-        <v>6395</v>
+        <v>22619</v>
       </c>
       <c r="M7" t="n">
-        <v>32825</v>
+        <v>86874</v>
       </c>
       <c r="N7" t="n">
-        <v>-648849</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+        <v>-6482919</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1387,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1401,47 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1975</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>-1</v>
+        <v>1415</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>1.07</v>
       </c>
       <c r="F8" t="n">
-        <v>57404</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>-19539</v>
+        <v>4142</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>409</v>
       </c>
       <c r="H8" t="n">
-        <v>-37942</v>
+        <v>-507</v>
       </c>
       <c r="I8" t="n">
-        <v>2624</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>8894</v>
+        <v>-16</v>
       </c>
       <c r="K8" t="n">
-        <v>1215</v>
+        <v>54</v>
       </c>
       <c r="L8" t="n">
-        <v>22619</v>
+        <v>1903</v>
       </c>
       <c r="M8" t="n">
-        <v>108149</v>
+        <v>7302</v>
       </c>
       <c r="N8" t="n">
-        <v>-6482919</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140153</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1450,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1464,47 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>124.5</v>
+        <v>1515</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.63</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>155981</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>22448</v>
+        <v>10658</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>-389</v>
       </c>
       <c r="H9" t="n">
-        <v>26982</v>
+        <v>-3122</v>
       </c>
       <c r="I9" t="n">
-        <v>951</v>
+        <v>522</v>
       </c>
       <c r="J9" t="n">
-        <v>25238</v>
+        <v>147</v>
       </c>
       <c r="K9" t="n">
-        <v>1504</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
-        <v>132443</v>
+        <v>2071</v>
       </c>
       <c r="M9" t="n">
-        <v>690462</v>
+        <v>5670</v>
       </c>
       <c r="N9" t="n">
-        <v>-1111395</v>
-      </c>
-      <c r="O9" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106265</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1539,13 +1646,13 @@
         <v>182</v>
       </c>
       <c r="H10" t="n">
-        <v>-1656</v>
+        <v>-450</v>
       </c>
       <c r="I10" t="n">
         <v>102</v>
       </c>
       <c r="J10" t="n">
-        <v>1440</v>
+        <v>556</v>
       </c>
       <c r="K10" t="n">
         <v>157</v>
@@ -1554,20 +1661,12 @@
         <v>1965</v>
       </c>
       <c r="M10" t="n">
-        <v>10930</v>
+        <v>8702</v>
       </c>
       <c r="N10" t="n">
         <v>-89480</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1576,12 +1675,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1590,47 +1689,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3440</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>-1.43</v>
+        <v>2355</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>9.789999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1581</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>125</v>
+        <v>3957</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>-608</v>
       </c>
       <c r="H11" t="n">
-        <v>698</v>
+        <v>148</v>
       </c>
       <c r="I11" t="n">
-        <v>-22</v>
+        <v>590</v>
       </c>
       <c r="J11" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="K11" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="L11" t="n">
-        <v>5771</v>
+        <v>4474</v>
       </c>
       <c r="M11" t="n">
-        <v>29259</v>
+        <v>16885</v>
       </c>
       <c r="N11" t="n">
-        <v>-19715</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19080</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1639,12 +1730,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1653,47 +1744,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2355</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>9.789999999999999</v>
+        <v>4775</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-6.65</v>
       </c>
       <c r="F12" t="n">
-        <v>3957</v>
+        <v>604</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>-608</v>
+        <v>-195</v>
       </c>
       <c r="H12" t="n">
-        <v>200</v>
+        <v>-53</v>
       </c>
       <c r="I12" t="n">
-        <v>590</v>
+        <v>-72</v>
       </c>
       <c r="J12" t="n">
+        <v>-39</v>
+      </c>
+      <c r="K12" t="n">
         <v>35</v>
       </c>
-      <c r="K12" t="n">
-        <v>66</v>
-      </c>
       <c r="L12" t="n">
-        <v>4474</v>
+        <v>332</v>
       </c>
       <c r="M12" t="n">
-        <v>20998</v>
+        <v>1357</v>
       </c>
       <c r="N12" t="n">
-        <v>-19080</v>
-      </c>
-      <c r="O12" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8887</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1716,25 +1799,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1390</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-5.76</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>6399</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>132</v>
       </c>
       <c r="H13" t="n">
-        <v>-466</v>
+        <v>-374</v>
       </c>
       <c r="I13" t="n">
         <v>143</v>
       </c>
       <c r="J13" t="n">
-        <v>-22</v>
+        <v>-28</v>
       </c>
       <c r="K13" t="n">
         <v>10</v>
@@ -1743,20 +1826,12 @@
         <v>122</v>
       </c>
       <c r="M13" t="n">
-        <v>-223</v>
+        <v>-215</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1765,12 +1840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1779,47 +1854,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>262</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-3.32</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>16580</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>-355</v>
+        <v>3871</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>963</v>
       </c>
       <c r="H14" t="n">
-        <v>-9540</v>
+        <v>2779</v>
       </c>
       <c r="I14" t="n">
-        <v>-441</v>
+        <v>1179</v>
       </c>
       <c r="J14" t="n">
-        <v>-3468</v>
+        <v>2844</v>
       </c>
       <c r="K14" t="n">
-        <v>454</v>
+        <v>-57</v>
       </c>
       <c r="L14" t="n">
-        <v>96</v>
+        <v>-322</v>
       </c>
       <c r="M14" t="n">
-        <v>487</v>
+        <v>-966</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1828,12 +1895,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1842,47 +1909,39 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>127</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-9.609999999999999</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>2433</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>-544</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>148</v>
       </c>
       <c r="H15" t="n">
-        <v>989</v>
+        <v>11602</v>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-151</v>
+        <v>79</v>
       </c>
       <c r="L15" t="n">
-        <v>95</v>
+        <v>-96</v>
       </c>
       <c r="M15" t="n">
-        <v>40</v>
+        <v>-145</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1891,12 +1950,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1905,543 +1964,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-9.9</v>
+        <v>1600</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>4583</v>
+        <v>904</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>963</v>
+        <v>94</v>
       </c>
       <c r="H16" t="n">
-        <v>1755</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1179</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>2798</v>
+        <v>-100</v>
       </c>
       <c r="K16" t="n">
-        <v>-57</v>
+        <v>-10</v>
       </c>
       <c r="L16" t="n">
-        <v>-322</v>
+        <v>-31</v>
       </c>
       <c r="M16" t="n">
-        <v>-1527</v>
+        <v>52</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-3.18</v>
-      </c>
-      <c r="F17" t="n">
-        <v>41298</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-3998</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-1341</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-113</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1995</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1261</v>
-      </c>
-      <c r="L17" t="n">
-        <v>19539</v>
-      </c>
-      <c r="M17" t="n">
-        <v>98779</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-113508</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6384</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>278</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-347</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>70</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5601</v>
-      </c>
-      <c r="M18" t="n">
-        <v>22351</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-11200</v>
-      </c>
-      <c r="O18" t="n">
-        <v>23.16</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1075</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>-4.87</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4623</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>731</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3405</v>
-      </c>
-      <c r="H19" t="n">
-        <v>66</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-40</v>
-      </c>
-      <c r="J19" t="n">
-        <v>262</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2246</v>
-      </c>
-      <c r="L19" t="n">
-        <v>12114</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-47592</v>
-      </c>
-      <c r="N19" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1415</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4142</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>409</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-98</v>
-      </c>
-      <c r="H20" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-11</v>
-      </c>
-      <c r="J20" t="n">
-        <v>54</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1903</v>
-      </c>
-      <c r="L20" t="n">
-        <v>9205</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-140153</v>
-      </c>
-      <c r="N20" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>962</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>826</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>94</v>
-      </c>
-      <c r="G21" t="n">
-        <v>114</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-31</v>
-      </c>
-      <c r="L21" t="n">
-        <v>21</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>624</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>148</v>
-      </c>
-      <c r="G22" t="n">
-        <v>11750</v>
-      </c>
-      <c r="H22" t="n">
-        <v>23</v>
-      </c>
-      <c r="I22" t="n">
-        <v>23</v>
-      </c>
-      <c r="J22" t="n">
-        <v>79</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-96</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-241</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1515</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="E23" t="n">
-        <v>10658</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>-389</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-3511</v>
-      </c>
-      <c r="H23" t="n">
-        <v>522</v>
-      </c>
-      <c r="I23" t="n">
-        <v>669</v>
-      </c>
-      <c r="J23" t="n">
-        <v>216</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2071</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7741</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-106265</v>
-      </c>
-      <c r="N23" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>245.5</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="E24" t="n">
-        <v>8576</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>649</v>
-      </c>
-      <c r="G24" t="n">
-        <v>4017</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I24" t="n">
-        <v>23</v>
-      </c>
-      <c r="J24" t="n">
-        <v>204</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8011</v>
-      </c>
-      <c r="L24" t="n">
-        <v>33235</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-58741</v>
-      </c>
-      <c r="N24" t="n">
-        <v>33.38</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4775</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>-6.65</v>
-      </c>
-      <c r="E25" t="n">
-        <v>604</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>-195</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-248</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-72</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-111</v>
-      </c>
-      <c r="J25" t="n">
-        <v>35</v>
-      </c>
-      <c r="K25" t="n">
-        <v>332</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1689</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-8887</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260302.xlsx
+++ b/outputs/monitor_xlsx/20260302.xlsx
@@ -544,10 +544,6 @@
           <t>-0.90%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-0.23%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+2.22%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+1.22%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.43%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+0.48%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>+7.96%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+6.28%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-389.89億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>125.36億</t>
@@ -807,7 +769,6 @@
           <t>83.22億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>33.09億</t>
@@ -818,8 +779,6 @@
           <t>165.45億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-432.14億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>14171口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>11909口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>-22.25億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-52.15億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1997,6 +1940,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>309</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1655</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-261</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>259</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6779</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33093</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21565</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.19</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260302.xlsx
+++ b/outputs/monitor_xlsx/20260302.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,26 +1245,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>80.34999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-0.99</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>224651</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-101500</v>
       </c>
       <c r="H4" t="n">
-        <v>-154795</v>
+        <v>-256295</v>
       </c>
       <c r="I4" t="n">
         <v>3214</v>
       </c>
       <c r="J4" t="n">
-        <v>21700</v>
+        <v>24914</v>
       </c>
       <c r="K4" t="n">
         <v>54837</v>
@@ -1274,11 +1273,14 @@
         <v>8643</v>
       </c>
       <c r="M4" t="n">
-        <v>32009</v>
+        <v>40652</v>
       </c>
       <c r="N4" t="n">
         <v>-4134246</v>
       </c>
+      <c r="O4" t="n">
+        <v>7.33</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1301,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>1030</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-3.74</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>3792</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-723</v>
       </c>
       <c r="H5" t="n">
-        <v>3148</v>
+        <v>2425</v>
       </c>
       <c r="I5" t="n">
         <v>39</v>
       </c>
       <c r="J5" t="n">
-        <v>-302</v>
+        <v>-263</v>
       </c>
       <c r="K5" t="n">
         <v>173</v>
@@ -1329,11 +1331,14 @@
         <v>2936</v>
       </c>
       <c r="M5" t="n">
-        <v>11898</v>
+        <v>14834</v>
       </c>
       <c r="N5" t="n">
         <v>-78749</v>
       </c>
+      <c r="O5" t="n">
+        <v>3.7</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1356,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1425</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-0.35</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>15569</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>210</v>
       </c>
       <c r="H6" t="n">
-        <v>2005</v>
+        <v>2215</v>
       </c>
       <c r="I6" t="n">
         <v>162</v>
       </c>
       <c r="J6" t="n">
-        <v>2486</v>
+        <v>2648</v>
       </c>
       <c r="K6" t="n">
         <v>337</v>
@@ -1384,11 +1389,14 @@
         <v>6395</v>
       </c>
       <c r="M6" t="n">
-        <v>26382</v>
+        <v>32777</v>
       </c>
       <c r="N6" t="n">
         <v>-648849</v>
       </c>
+      <c r="O6" t="n">
+        <v>12.85</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1411,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1975</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-1</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>57404</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-19539</v>
       </c>
       <c r="H7" t="n">
-        <v>-33001</v>
+        <v>-52539</v>
       </c>
       <c r="I7" t="n">
         <v>2624</v>
       </c>
       <c r="J7" t="n">
-        <v>7753</v>
+        <v>10377</v>
       </c>
       <c r="K7" t="n">
         <v>1215</v>
@@ -1439,11 +1447,14 @@
         <v>22619</v>
       </c>
       <c r="M7" t="n">
-        <v>86874</v>
+        <v>109493</v>
       </c>
       <c r="N7" t="n">
         <v>-6482919</v>
       </c>
+      <c r="O7" t="n">
+        <v>7.28</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1466,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>1415</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>1.07</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>4142</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>409</v>
       </c>
       <c r="H8" t="n">
-        <v>-507</v>
+        <v>-98</v>
       </c>
       <c r="I8" t="n">
         <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="K8" t="n">
         <v>54</v>
@@ -1494,11 +1505,14 @@
         <v>1903</v>
       </c>
       <c r="M8" t="n">
-        <v>7302</v>
+        <v>9205</v>
       </c>
       <c r="N8" t="n">
         <v>-140153</v>
       </c>
+      <c r="O8" t="n">
+        <v>12.64</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1521,26 +1535,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1515</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>10658</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>-389</v>
       </c>
       <c r="H9" t="n">
-        <v>-3122</v>
+        <v>-3511</v>
       </c>
       <c r="I9" t="n">
         <v>522</v>
       </c>
       <c r="J9" t="n">
-        <v>147</v>
+        <v>669</v>
       </c>
       <c r="K9" t="n">
         <v>216</v>
@@ -1549,11 +1563,14 @@
         <v>2071</v>
       </c>
       <c r="M9" t="n">
-        <v>5670</v>
+        <v>7741</v>
       </c>
       <c r="N9" t="n">
         <v>-106265</v>
       </c>
+      <c r="O9" t="n">
+        <v>39.33</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1576,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2380</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-2.46</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>3331</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>182</v>
       </c>
       <c r="H10" t="n">
-        <v>-450</v>
+        <v>-268</v>
       </c>
       <c r="I10" t="n">
         <v>102</v>
       </c>
       <c r="J10" t="n">
-        <v>556</v>
+        <v>658</v>
       </c>
       <c r="K10" t="n">
         <v>157</v>
@@ -1604,11 +1621,14 @@
         <v>1965</v>
       </c>
       <c r="M10" t="n">
-        <v>8702</v>
+        <v>10667</v>
       </c>
       <c r="N10" t="n">
         <v>-89480</v>
       </c>
+      <c r="O10" t="n">
+        <v>18.66</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1631,26 +1651,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>2355</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>3957</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>-608</v>
       </c>
       <c r="H11" t="n">
-        <v>148</v>
+        <v>-459</v>
       </c>
       <c r="I11" t="n">
         <v>590</v>
       </c>
       <c r="J11" t="n">
-        <v>40</v>
+        <v>630</v>
       </c>
       <c r="K11" t="n">
         <v>66</v>
@@ -1659,11 +1679,14 @@
         <v>4474</v>
       </c>
       <c r="M11" t="n">
-        <v>16885</v>
+        <v>21359</v>
       </c>
       <c r="N11" t="n">
         <v>-19080</v>
       </c>
+      <c r="O11" t="n">
+        <v>31.79</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1686,26 +1709,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>4775</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>-6.65</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>604</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>-195</v>
       </c>
       <c r="H12" t="n">
-        <v>-53</v>
+        <v>-248</v>
       </c>
       <c r="I12" t="n">
         <v>-72</v>
       </c>
       <c r="J12" t="n">
-        <v>-39</v>
+        <v>-111</v>
       </c>
       <c r="K12" t="n">
         <v>35</v>
@@ -1714,11 +1737,14 @@
         <v>332</v>
       </c>
       <c r="M12" t="n">
-        <v>1357</v>
+        <v>1689</v>
       </c>
       <c r="N12" t="n">
         <v>-8887</v>
       </c>
+      <c r="O12" t="n">
+        <v>7.55</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1741,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>132</v>
       </c>
       <c r="H13" t="n">
-        <v>-374</v>
+        <v>-241</v>
       </c>
       <c r="I13" t="n">
         <v>143</v>
       </c>
       <c r="J13" t="n">
-        <v>-28</v>
+        <v>115</v>
       </c>
       <c r="K13" t="n">
         <v>10</v>
@@ -1769,11 +1795,14 @@
         <v>122</v>
       </c>
       <c r="M13" t="n">
-        <v>-215</v>
+        <v>-93</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1796,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>963</v>
       </c>
       <c r="H14" t="n">
-        <v>2779</v>
+        <v>3742</v>
       </c>
       <c r="I14" t="n">
         <v>1179</v>
       </c>
       <c r="J14" t="n">
-        <v>2844</v>
+        <v>4024</v>
       </c>
       <c r="K14" t="n">
         <v>-57</v>
@@ -1824,11 +1853,14 @@
         <v>-322</v>
       </c>
       <c r="M14" t="n">
-        <v>-966</v>
+        <v>-1288</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1851,26 +1883,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>148</v>
       </c>
       <c r="H15" t="n">
-        <v>11602</v>
+        <v>11750</v>
       </c>
       <c r="I15" t="n">
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
         <v>79</v>
@@ -1879,11 +1911,14 @@
         <v>-96</v>
       </c>
       <c r="M15" t="n">
-        <v>-145</v>
+        <v>-241</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1906,20 +1941,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>94</v>
       </c>
       <c r="H16" t="n">
-        <v>20</v>
+        <v>114</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-100</v>
@@ -1931,11 +1969,14 @@
         <v>-31</v>
       </c>
       <c r="M16" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1953,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>309</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>4.04</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1655</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>-2</v>
       </c>
-      <c r="G17" t="n">
-        <v>-261</v>
-      </c>
       <c r="H17" t="n">
+        <v>-168</v>
+      </c>
+      <c r="I17" t="n">
         <v>-3</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>259</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>16</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>6779</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>33093</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-21565</v>
       </c>
-      <c r="N17" t="n">
-        <v>7.19</v>
+      <c r="O17" t="n">
+        <v>25.57</v>
       </c>
     </row>
   </sheetData>
